--- a/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
+++ b/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
@@ -7865,7 +7865,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8055,7 +8055,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8226,7 +8226,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8400,7 +8400,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8576,7 +8576,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8841,7 +8841,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9125,7 +9125,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9371,7 +9371,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9485,7 +9485,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9769,7 +9769,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9996,7 +9996,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10204,7 +10204,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10278,7 +10278,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10468,7 +10468,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10620,7 +10620,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10753,7 +10753,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
+++ b/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
@@ -7865,7 +7865,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.5.xlsx</t>
+      <t xml:space="preserve">_v0.5.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8055,7 +8055,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.5.xlsx</t>
+      <t xml:space="preserve">_v0.5.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8226,7 +8226,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.5.xlsx</t>
+      <t xml:space="preserve">_v0.5.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8400,7 +8400,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.5.xlsx</t>
+      <t xml:space="preserve">_v0.5.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8576,7 +8576,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8841,7 +8841,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9125,7 +9125,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9371,7 +9371,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9485,7 +9485,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9769,7 +9769,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9996,7 +9996,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10204,7 +10204,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10278,7 +10278,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10468,7 +10468,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10620,7 +10620,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10753,7 +10753,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
+++ b/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
@@ -10259,26 +10259,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10449,26 +10449,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10601,26 +10601,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10734,26 +10734,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
+++ b/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
@@ -8557,26 +8557,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8822,26 +8822,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9106,26 +9106,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9352,26 +9352,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9466,26 +9466,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星電子模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三星電子個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9750,26 +9750,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星電子模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三星電子個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9977,26 +9977,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星電子模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三星電子個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10185,26 +10185,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星電子模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三星電子個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
+++ b/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
@@ -7846,26 +7846,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8036,26 +8036,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8207,26 +8207,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8381,26 +8381,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
+++ b/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
@@ -7846,7 +7846,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261029_SK</t>
+      <t xml:space="preserve">20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -7865,7 +7865,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8036,7 +8036,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261029_SK</t>
+      <t xml:space="preserve">20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -8055,7 +8055,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8207,7 +8207,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261029_SK</t>
+      <t xml:space="preserve">20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -8226,7 +8226,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8381,7 +8381,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261029_SK</t>
+      <t xml:space="preserve">20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -8400,7 +8400,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8557,7 +8557,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8576,7 +8576,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8822,7 +8822,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8841,7 +8841,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9106,7 +9106,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9125,7 +9125,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9352,7 +9352,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9371,7 +9371,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9466,7 +9466,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9485,7 +9485,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9750,7 +9750,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9769,7 +9769,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9977,7 +9977,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9996,7 +9996,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10185,7 +10185,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -10204,7 +10204,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10259,7 +10259,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -10278,7 +10278,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10449,7 +10449,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -10468,7 +10468,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10601,7 +10601,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -10620,7 +10620,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10734,7 +10734,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261028_</t>
+      <t xml:space="preserve">20261030_</t>
     </r>
     <r>
       <rPr>
@@ -10753,7 +10753,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
+++ b/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.3.xlsx
@@ -9485,7 +9485,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.3.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9572,26 +9572,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">｜全公司約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">70</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（首爾經濟日報）</t>
+      <t xml:space="preserve">｜公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：全年約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兆（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DS 76.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SDC 3.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
     <r>
       <rPr>
@@ -9648,6 +9705,63 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.3.3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 75%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">）；全公司</t>
     </r>
     <r>
@@ -9769,7 +9883,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.3.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9996,7 +10110,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.3.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10204,7 +10318,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.3.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -43319,7 +43433,7 @@
         <v>78</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>52.5</v>
+        <v>63.3</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>114</v>
@@ -45359,7 +45473,7 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">D129</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="E6" s="17" t="n">
         <f aca="false">E129</f>
@@ -45383,11 +45497,11 @@
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">D130</f>
-        <v>0.322725497972614</v>
+        <v>0.351591651867038</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">E130</f>
-        <v>0.224905413856655</v>
+        <v>0.198744917723333</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">F130</f>
@@ -45411,7 +45525,7 @@
       </c>
       <c r="D8" s="17" t="n">
         <f aca="false">D127</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E8" s="17" t="n">
         <f aca="false">E127</f>
@@ -45439,7 +45553,7 @@
       </c>
       <c r="D9" s="17" t="n">
         <f aca="false">D132</f>
-        <v>93.0407901320055</v>
+        <v>95.5491280580347</v>
       </c>
       <c r="E9" s="17" t="n">
         <f aca="false">E132</f>
@@ -45463,7 +45577,7 @@
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">D134</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">E134</f>
@@ -45487,11 +45601,11 @@
       </c>
       <c r="D11" s="19" t="n">
         <f aca="false">D135</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">E135</f>
-        <v>0.61868486681369</v>
+        <v>0.615840420051635</v>
       </c>
       <c r="F11" s="19" t="n">
         <f aca="false">F135</f>
@@ -45529,7 +45643,7 @@
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">D148</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="E14" s="17" t="n">
         <f aca="false">E148</f>
@@ -45553,11 +45667,11 @@
       </c>
       <c r="D15" s="18" t="n">
         <f aca="false">D149</f>
-        <v>0.322725497972614</v>
+        <v>0.351591651867038</v>
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">E149</f>
-        <v>0.224905413856655</v>
+        <v>0.198744917723333</v>
       </c>
       <c r="F15" s="18" t="n">
         <f aca="false">F149</f>
@@ -45581,7 +45695,7 @@
       </c>
       <c r="D16" s="17" t="n">
         <f aca="false">D146</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">E146</f>
@@ -45609,7 +45723,7 @@
       </c>
       <c r="D17" s="17" t="n">
         <f aca="false">D151</f>
-        <v>93.0407901320055</v>
+        <v>95.5491280580347</v>
       </c>
       <c r="E17" s="17" t="n">
         <f aca="false">E151</f>
@@ -45633,7 +45747,7 @@
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">D153</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E18" s="19" t="n">
         <f aca="false">E153</f>
@@ -45657,11 +45771,11 @@
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">D154</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E19" s="19" t="n">
         <f aca="false">E154</f>
-        <v>0.61868486681369</v>
+        <v>0.615840420051635</v>
       </c>
       <c r="F19" s="19" t="str">
         <f aca="false">F154</f>
@@ -45699,7 +45813,7 @@
       </c>
       <c r="D22" s="17" t="n">
         <f aca="false">D167</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="E22" s="17" t="n">
         <f aca="false">E167</f>
@@ -45723,11 +45837,11 @@
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">D168</f>
-        <v>0.322725497972614</v>
+        <v>0.351591651867038</v>
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">E168</f>
-        <v>0.224905413856655</v>
+        <v>0.198744917723333</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">F168</f>
@@ -45751,7 +45865,7 @@
       </c>
       <c r="D24" s="17" t="n">
         <f aca="false">D165</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E24" s="17" t="n">
         <f aca="false">E165</f>
@@ -45779,7 +45893,7 @@
       </c>
       <c r="D25" s="17" t="n">
         <f aca="false">D170</f>
-        <v>93.0407901320055</v>
+        <v>95.5491280580347</v>
       </c>
       <c r="E25" s="17" t="n">
         <f aca="false">E170</f>
@@ -45803,7 +45917,7 @@
       </c>
       <c r="D26" s="19" t="n">
         <f aca="false">D172</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">E172</f>
@@ -45827,11 +45941,11 @@
       </c>
       <c r="D27" s="19" t="n">
         <f aca="false">D173</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E27" s="19" t="n">
         <f aca="false">E173</f>
-        <v>0.61868486681369</v>
+        <v>0.615840420051635</v>
       </c>
       <c r="F27" s="19" t="n">
         <f aca="false">F173</f>
@@ -46392,7 +46506,7 @@
       </c>
       <c r="D69" s="17" t="n">
         <f aca="false">cap_ss_26*1000/fx</f>
-        <v>36.9718309859155</v>
+        <v>44.5774647887324</v>
       </c>
       <c r="E69" s="17" t="n">
         <f aca="false">cap_ss_27*1000/fx</f>
@@ -46423,7 +46537,7 @@
       </c>
       <c r="D70" s="17" t="n">
         <f aca="false">D67+D68+D69</f>
-        <v>98.6346056338028</v>
+        <v>106.24023943662</v>
       </c>
       <c r="E70" s="17" t="n">
         <f aca="false">E67+E68+E69</f>
@@ -46628,7 +46742,7 @@
       </c>
       <c r="D86" s="17" t="n">
         <f aca="false">D69*sh_ss</f>
-        <v>16.8389314726833</v>
+        <v>20.3029402327782</v>
       </c>
       <c r="E86" s="17" t="n">
         <f aca="false">E69*sh_ss</f>
@@ -46656,7 +46770,7 @@
       </c>
       <c r="D87" s="17" t="n">
         <f aca="false">D84+D85+D86</f>
-        <v>46.7172520482963</v>
+        <v>50.1812608083911</v>
       </c>
       <c r="E87" s="17" t="n">
         <f aca="false">E84+E85+E86</f>
@@ -46684,7 +46798,7 @@
       </c>
       <c r="D88" s="18" t="n">
         <f aca="false">D87/D70</f>
-        <v>0.47363956846689</v>
+        <v>0.472337610254804</v>
       </c>
       <c r="E88" s="18" t="n">
         <f aca="false">E87/E70</f>
@@ -46712,7 +46826,7 @@
       </c>
       <c r="D89" s="17" t="n">
         <f aca="false">D87*D49</f>
-        <v>33.8286255111531</v>
+        <v>36.3369634371822</v>
       </c>
       <c r="E89" s="17" t="n">
         <f aca="false">E87*E49</f>
@@ -46743,7 +46857,7 @@
       </c>
       <c r="D90" s="17" t="n">
         <f aca="false">D87-D89</f>
-        <v>12.8886265371432</v>
+        <v>13.8442973712089</v>
       </c>
       <c r="E90" s="17" t="n">
         <f aca="false">E87-E89</f>
@@ -46827,7 +46941,7 @@
       </c>
       <c r="D93" s="17" t="n">
         <f aca="false">D87+D91+D92</f>
-        <v>56.8698522719522</v>
+        <v>60.333861032047</v>
       </c>
       <c r="E93" s="17" t="n">
         <f aca="false">E87+E91+E92</f>
@@ -46867,7 +46981,7 @@
       </c>
       <c r="D95" s="17" t="n">
         <f aca="false">D93-D41-D42</f>
-        <v>4.16985227195219</v>
+        <v>7.63386103204704</v>
       </c>
       <c r="E95" s="17" t="n">
         <f aca="false">E93-E41-E42</f>
@@ -47066,7 +47180,7 @@
       </c>
       <c r="D106" s="17" t="n">
         <f aca="false">D50*(D93+D102)</f>
-        <v>17.0278249760553</v>
+        <v>17.4517800051339</v>
       </c>
       <c r="E106" s="17" t="n">
         <f aca="false">E50*(E93+E102)</f>
@@ -47280,7 +47394,7 @@
       </c>
       <c r="D122" s="17" t="n">
         <f aca="false">D89+D91</f>
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="E122" s="17" t="n">
         <f aca="false">E89+E91</f>
@@ -47308,7 +47422,7 @@
       </c>
       <c r="D123" s="17" t="n">
         <f aca="false">D90+D92</f>
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="E123" s="17" t="n">
         <f aca="false">E90+E92</f>
@@ -47336,7 +47450,7 @@
       </c>
       <c r="D124" s="17" t="n">
         <f aca="false">D106</f>
-        <v>17.0278249760553</v>
+        <v>17.4517800051339</v>
       </c>
       <c r="E124" s="17" t="n">
         <f aca="false">E106</f>
@@ -47420,7 +47534,7 @@
       </c>
       <c r="D127" s="17" t="n">
         <f aca="false">SUM(D120:D124)</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E127" s="17" t="n">
         <f aca="false">SUM(E120:E124)</f>
@@ -47476,7 +47590,7 @@
       </c>
       <c r="D129" s="17" t="n">
         <f aca="false">D127+D128</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="E129" s="17" t="n">
         <f aca="false">E127+E128</f>
@@ -47500,11 +47614,11 @@
       </c>
       <c r="D130" s="18" t="n">
         <f aca="false">D129/C129-1</f>
-        <v>0.322725497972614</v>
+        <v>0.351591651867038</v>
       </c>
       <c r="E130" s="18" t="n">
         <f aca="false">E129/D129-1</f>
-        <v>0.224905413856655</v>
+        <v>0.198744917723333</v>
       </c>
       <c r="F130" s="18" t="n">
         <f aca="false">F129/E129-1</f>
@@ -47527,11 +47641,11 @@
       </c>
       <c r="D131" s="18" t="n">
         <f aca="false">D127/C127-1</f>
-        <v>0.335853573674957</v>
+        <v>0.369113361197351</v>
       </c>
       <c r="E131" s="18" t="n">
         <f aca="false">E127/D127-1</f>
-        <v>0.234625453501252</v>
+        <v>0.204632772531957</v>
       </c>
       <c r="F131" s="18" t="n">
         <f aca="false">F127/E127-1</f>
@@ -47555,7 +47669,7 @@
       </c>
       <c r="D132" s="17" t="n">
         <f aca="false">D120+D122+D125</f>
-        <v>93.0407901320055</v>
+        <v>95.5491280580347</v>
       </c>
       <c r="E132" s="17" t="n">
         <f aca="false">E120+E122+E125</f>
@@ -47583,7 +47697,7 @@
       </c>
       <c r="D133" s="18" t="n">
         <f aca="false">D132/D129</f>
-        <v>0.522240292114526</v>
+        <v>0.524865393289213</v>
       </c>
       <c r="E133" s="18" t="n">
         <f aca="false">E132/E129</f>
@@ -47607,7 +47721,7 @@
       </c>
       <c r="D134" s="19" t="n">
         <f aca="false">IF(ABS(D129-C129)&lt;0.05,"n/a",(D132-C132)/(D129-C129))</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E134" s="19" t="n">
         <f aca="false">IF(ABS(E129-C129)&lt;0.05,"n/a",(E132-C132)/(E129-C129))</f>
@@ -47634,11 +47748,11 @@
       </c>
       <c r="D135" s="19" t="n">
         <f aca="false">IF(ABS(D129-C129)&lt;0.05,"n/a",(D132-C132)/(D129-C129))</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E135" s="19" t="n">
         <f aca="false">IF(ABS(E129-D129)&lt;0.05,"n/a",(E132-D132)/(E129-D129))</f>
-        <v>0.61868486681369</v>
+        <v>0.615840420051635</v>
       </c>
       <c r="F135" s="19" t="n">
         <f aca="false">IF(ABS(F129-E129)&lt;0.05,"n/a",(F132-E132)/(F129-E129))</f>
@@ -47741,7 +47855,7 @@
       </c>
       <c r="D141" s="17" t="n">
         <f aca="false">D122</f>
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="E141" s="17" t="n">
         <f aca="false">E122</f>
@@ -47769,7 +47883,7 @@
       </c>
       <c r="D142" s="17" t="n">
         <f aca="false">D123</f>
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="E142" s="17" t="n">
         <f aca="false">E123</f>
@@ -47797,7 +47911,7 @@
       </c>
       <c r="D143" s="17" t="n">
         <f aca="false">D124</f>
-        <v>17.0278249760553</v>
+        <v>17.4517800051339</v>
       </c>
       <c r="E143" s="17" t="n">
         <f aca="false">E124</f>
@@ -47881,7 +47995,7 @@
       </c>
       <c r="D146" s="17" t="n">
         <f aca="false">SUM(D139:D143)</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E146" s="17" t="n">
         <f aca="false">SUM(E139:E143)</f>
@@ -47937,7 +48051,7 @@
       </c>
       <c r="D148" s="17" t="n">
         <f aca="false">D146+D147</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="E148" s="17" t="n">
         <f aca="false">E146+E147</f>
@@ -47961,11 +48075,11 @@
       </c>
       <c r="D149" s="18" t="n">
         <f aca="false">D148/C148-1</f>
-        <v>0.322725497972614</v>
+        <v>0.351591651867038</v>
       </c>
       <c r="E149" s="18" t="n">
         <f aca="false">E148/D148-1</f>
-        <v>0.224905413856655</v>
+        <v>0.198744917723333</v>
       </c>
       <c r="F149" s="18" t="n">
         <f aca="false">F148/E148-1</f>
@@ -47988,11 +48102,11 @@
       </c>
       <c r="D150" s="18" t="n">
         <f aca="false">D146/C146-1</f>
-        <v>0.335853573674957</v>
+        <v>0.369113361197351</v>
       </c>
       <c r="E150" s="18" t="n">
         <f aca="false">E146/D146-1</f>
-        <v>0.234625453501252</v>
+        <v>0.204632772531957</v>
       </c>
       <c r="F150" s="18" t="n">
         <f aca="false">F146/E146-1</f>
@@ -48016,7 +48130,7 @@
       </c>
       <c r="D151" s="17" t="n">
         <f aca="false">D139+D141+D144</f>
-        <v>93.0407901320055</v>
+        <v>95.5491280580347</v>
       </c>
       <c r="E151" s="17" t="n">
         <f aca="false">E139+E141+E144</f>
@@ -48044,7 +48158,7 @@
       </c>
       <c r="D152" s="18" t="n">
         <f aca="false">D151/D148</f>
-        <v>0.522240292114526</v>
+        <v>0.524865393289213</v>
       </c>
       <c r="E152" s="18" t="n">
         <f aca="false">E151/E148</f>
@@ -48068,7 +48182,7 @@
       </c>
       <c r="D153" s="19" t="n">
         <f aca="false">IF(ABS(D148-C148)&lt;0.05,"n/a",(D151-C151)/(D148-C148))</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E153" s="19" t="n">
         <f aca="false">IF(ABS(E148-C148)&lt;0.05,"n/a",(E151-C151)/(E148-C148))</f>
@@ -48095,11 +48209,11 @@
       </c>
       <c r="D154" s="19" t="n">
         <f aca="false">IF(ABS(D148-C148)&lt;0.05,"n/a",(D151-C151)/(D148-C148))</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E154" s="19" t="n">
         <f aca="false">IF(ABS(E148-D148)&lt;0.05,"n/a",(E151-D151)/(E148-D148))</f>
-        <v>0.61868486681369</v>
+        <v>0.615840420051635</v>
       </c>
       <c r="F154" s="19" t="str">
         <f aca="false">IF(ABS(F148-E148)&lt;0.05,"n/a",(F151-E151)/(F148-E148))</f>
@@ -48202,7 +48316,7 @@
       </c>
       <c r="D160" s="17" t="n">
         <f aca="false">D122</f>
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="E160" s="17" t="n">
         <f aca="false">E122</f>
@@ -48230,7 +48344,7 @@
       </c>
       <c r="D161" s="17" t="n">
         <f aca="false">D123</f>
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="E161" s="17" t="n">
         <f aca="false">E123</f>
@@ -48258,7 +48372,7 @@
       </c>
       <c r="D162" s="17" t="n">
         <f aca="false">D124</f>
-        <v>17.0278249760553</v>
+        <v>17.4517800051339</v>
       </c>
       <c r="E162" s="17" t="n">
         <f aca="false">E124</f>
@@ -48342,7 +48456,7 @@
       </c>
       <c r="D165" s="17" t="n">
         <f aca="false">SUM(D158:D162)</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E165" s="17" t="n">
         <f aca="false">SUM(E158:E162)</f>
@@ -48398,7 +48512,7 @@
       </c>
       <c r="D167" s="17" t="n">
         <f aca="false">D165+D166</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="E167" s="17" t="n">
         <f aca="false">E165+E166</f>
@@ -48422,11 +48536,11 @@
       </c>
       <c r="D168" s="18" t="n">
         <f aca="false">D167/C167-1</f>
-        <v>0.322725497972614</v>
+        <v>0.351591651867038</v>
       </c>
       <c r="E168" s="18" t="n">
         <f aca="false">E167/D167-1</f>
-        <v>0.224905413856655</v>
+        <v>0.198744917723333</v>
       </c>
       <c r="F168" s="18" t="n">
         <f aca="false">F167/E167-1</f>
@@ -48449,11 +48563,11 @@
       </c>
       <c r="D169" s="18" t="n">
         <f aca="false">D165/C165-1</f>
-        <v>0.335853573674957</v>
+        <v>0.369113361197351</v>
       </c>
       <c r="E169" s="18" t="n">
         <f aca="false">E165/D165-1</f>
-        <v>0.234625453501252</v>
+        <v>0.204632772531957</v>
       </c>
       <c r="F169" s="18" t="n">
         <f aca="false">F165/E165-1</f>
@@ -48477,7 +48591,7 @@
       </c>
       <c r="D170" s="17" t="n">
         <f aca="false">D158+D160+D163</f>
-        <v>93.0407901320055</v>
+        <v>95.5491280580347</v>
       </c>
       <c r="E170" s="17" t="n">
         <f aca="false">E158+E160+E163</f>
@@ -48505,7 +48619,7 @@
       </c>
       <c r="D171" s="18" t="n">
         <f aca="false">D170/D167</f>
-        <v>0.522240292114526</v>
+        <v>0.524865393289213</v>
       </c>
       <c r="E171" s="18" t="n">
         <f aca="false">E170/E167</f>
@@ -48529,7 +48643,7 @@
       </c>
       <c r="D172" s="19" t="n">
         <f aca="false">IF(ABS(D167-C167)&lt;0.05,"n/a",(D170-C170)/(D167-C167))</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E172" s="19" t="n">
         <f aca="false">IF(ABS(E167-C167)&lt;0.05,"n/a",(E170-C170)/(E167-C167))</f>
@@ -48556,11 +48670,11 @@
       </c>
       <c r="D173" s="19" t="n">
         <f aca="false">IF(ABS(D167-C167)&lt;0.05,"n/a",(D170-C170)/(D167-C167))</f>
-        <v>0.634397060086663</v>
+        <v>0.635280273060519</v>
       </c>
       <c r="E173" s="19" t="n">
         <f aca="false">IF(ABS(E167-D167)&lt;0.05,"n/a",(E170-D170)/(E167-D167))</f>
-        <v>0.61868486681369</v>
+        <v>0.615840420051635</v>
       </c>
       <c r="F173" s="19" t="n">
         <f aca="false">IF(ABS(F167-E167)&lt;0.05,"n/a",(F170-E170)/(F167-E167))</f>
@@ -49692,15 +49806,15 @@
       </c>
       <c r="B60" s="18" t="n">
         <f aca="false">B59/Mkt!D129</f>
-        <v>0.0222724836727026</v>
+        <v>0.0217968067621363</v>
       </c>
       <c r="C60" s="18" t="n">
         <f aca="false">C59/Mkt!D129</f>
-        <v>0.0334087255090539</v>
+        <v>0.0326952101432045</v>
       </c>
       <c r="D60" s="18" t="n">
         <f aca="false">D59/Mkt!D129</f>
-        <v>0.0445449673454052</v>
+        <v>0.0435936135242726</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49799,27 +49913,27 @@
       </c>
       <c r="E4" s="17" t="n">
         <f aca="false">Mkt!D129</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">E4/D4-1</f>
-        <v>0.0738821613630314</v>
+        <v>0.0973177477956622</v>
       </c>
       <c r="G4" s="17" t="n">
         <f aca="false">Mkt!D148</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="H4" s="18" t="n">
         <f aca="false">G4/D4-1</f>
-        <v>0.0738821613630314</v>
+        <v>0.0973177477956622</v>
       </c>
       <c r="I4" s="17" t="n">
         <f aca="false">Mkt!D167</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="J4" s="18" t="n">
         <f aca="false">I4/D4-1</f>
-        <v>0.0738821613630314</v>
+        <v>0.0973177477956622</v>
       </c>
       <c r="K4" s="0" t="str">
         <f aca="false">IF(ABS(F4)&gt;rc_thr,"超過門檻","")</f>
@@ -49845,27 +49959,27 @@
       </c>
       <c r="E5" s="17" t="n">
         <f aca="false">Mkt!D127</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">E5/D5-1</f>
-        <v>0.0851775578188112</v>
+        <v>0.11219606920987</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">Mkt!D146</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="H5" s="18" t="n">
         <f aca="false">G5/D5-1</f>
-        <v>0.0851775578188112</v>
+        <v>0.11219606920987</v>
       </c>
       <c r="I5" s="17" t="n">
         <f aca="false">Mkt!D165</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="J5" s="18" t="n">
         <f aca="false">I5/D5-1</f>
-        <v>0.0851775578188112</v>
+        <v>0.11219606920987</v>
       </c>
       <c r="K5" s="0" t="str">
         <f aca="false">IF(ABS(F5)&gt;rc_thr,"超過門檻","")</f>
@@ -49934,27 +50048,27 @@
       </c>
       <c r="E7" s="17" t="n">
         <f aca="false">Mkt!D122</f>
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">E7/D7-1</f>
-        <v>0.014586257769992</v>
+        <v>0.0792341424614638</v>
       </c>
       <c r="G7" s="17" t="n">
         <f aca="false">Mkt!D141</f>
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="H7" s="18" t="n">
         <f aca="false">G7/D7-1</f>
-        <v>0.014586257769992</v>
+        <v>0.0792341424614638</v>
       </c>
       <c r="I7" s="17" t="n">
         <f aca="false">Mkt!D160</f>
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="J7" s="18" t="n">
         <f aca="false">I7/D7-1</f>
-        <v>0.014586257769992</v>
+        <v>0.0792341424614638</v>
       </c>
       <c r="K7" s="0" t="str">
         <f aca="false">IF(ABS(F7)&gt;rc_thr,"超過門檻","")</f>
@@ -49980,27 +50094,27 @@
       </c>
       <c r="E8" s="17" t="n">
         <f aca="false">Mkt!D123</f>
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">E8/D8-1</f>
-        <v>0.259273774854424</v>
+        <v>0.328027072269226</v>
       </c>
       <c r="G8" s="17" t="n">
         <f aca="false">Mkt!D142</f>
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="H8" s="18" t="n">
         <f aca="false">G8/D8-1</f>
-        <v>0.259273774854424</v>
+        <v>0.328027072269226</v>
       </c>
       <c r="I8" s="17" t="n">
         <f aca="false">Mkt!D161</f>
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="J8" s="18" t="n">
         <f aca="false">I8/D8-1</f>
-        <v>0.259273774854424</v>
+        <v>0.328027072269226</v>
       </c>
       <c r="K8" s="0" t="str">
         <f aca="false">IF(ABS(F8)&gt;rc_thr,"超過門檻","")</f>
@@ -50023,27 +50137,27 @@
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">Mkt!E131</f>
-        <v>0.234625453501252</v>
+        <v>0.204632772531957</v>
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">E9-D9</f>
-        <v>0.0166254535012517</v>
+        <v>-0.013367227468043</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">Mkt!E150</f>
-        <v>0.234625453501252</v>
+        <v>0.204632772531957</v>
       </c>
       <c r="H9" s="18" t="n">
         <f aca="false">G9-D9</f>
-        <v>0.0166254535012517</v>
+        <v>-0.013367227468043</v>
       </c>
       <c r="I9" s="18" t="n">
         <f aca="false">Mkt!E169</f>
-        <v>0.234625453501252</v>
+        <v>0.204632772531957</v>
       </c>
       <c r="J9" s="18" t="n">
         <f aca="false">I9-D9</f>
-        <v>0.0166254535012517</v>
+        <v>-0.013367227468043</v>
       </c>
       <c r="K9" s="0" t="str">
         <f aca="false">IF(ABS(F9)&gt;0.05,"超過 5 個百分點","")</f>
@@ -50207,27 +50321,27 @@
       </c>
       <c r="E13" s="17" t="n">
         <f aca="false">Mkt!D127</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">E13/D13-1</f>
-        <v>0.0410470038008461</v>
+        <v>0.0669667623953356</v>
       </c>
       <c r="G13" s="17" t="n">
         <f aca="false">Mkt!D146</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="H13" s="18" t="n">
         <f aca="false">G13/D13-1</f>
-        <v>0.0410470038008461</v>
+        <v>0.0669667623953356</v>
       </c>
       <c r="I13" s="17" t="n">
         <f aca="false">Mkt!D165</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="J13" s="18" t="n">
         <f aca="false">I13/D13-1</f>
-        <v>0.0410470038008461</v>
+        <v>0.0669667623953356</v>
       </c>
       <c r="K13" s="0" t="str">
         <f aca="false">IF(ABS(F13)&gt;rc_thr,"超過門檻","")</f>
@@ -50253,27 +50367,27 @@
       </c>
       <c r="E14" s="17" t="n">
         <f aca="false">Mkt!D127</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">E14/D14-1</f>
-        <v>0.0410470038008461</v>
+        <v>0.0669667623953356</v>
       </c>
       <c r="G14" s="17" t="n">
         <f aca="false">Mkt!D146</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="H14" s="18" t="n">
         <f aca="false">G14/D14-1</f>
-        <v>0.0410470038008461</v>
+        <v>0.0669667623953356</v>
       </c>
       <c r="I14" s="17" t="n">
         <f aca="false">Mkt!D165</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="J14" s="18" t="n">
         <f aca="false">I14/D14-1</f>
-        <v>0.0410470038008461</v>
+        <v>0.0669667623953356</v>
       </c>
       <c r="K14" s="0" t="str">
         <f aca="false">IF(ABS(F14)&gt;rc_thr,"超過門檻","")</f>
@@ -50480,27 +50594,27 @@
       </c>
       <c r="E19" s="17" t="n">
         <f aca="false">Mkt!D127</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">E19/D19-1</f>
-        <v>0.0410470038008461</v>
+        <v>0.0669667623953356</v>
       </c>
       <c r="G19" s="17" t="n">
         <f aca="false">Mkt!D146</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="H19" s="18" t="n">
         <f aca="false">G19/D19-1</f>
-        <v>0.0410470038008461</v>
+        <v>0.0669667623953356</v>
       </c>
       <c r="I19" s="17" t="n">
         <f aca="false">Mkt!D165</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="J19" s="18" t="n">
         <f aca="false">I19/D19-1</f>
-        <v>0.0410470038008461</v>
+        <v>0.0669667623953356</v>
       </c>
       <c r="K19" s="0" t="str">
         <f aca="false">IF(ABS(F19)&gt;rc_thr,"超過門檻","")</f>
@@ -51833,7 +51947,7 @@
       </c>
       <c r="C44" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="D44" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -51862,7 +51976,7 @@
       </c>
       <c r="C45" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="D45" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -51891,7 +52005,7 @@
       </c>
       <c r="C46" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="D46" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -51920,7 +52034,7 @@
       </c>
       <c r="C47" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_oth+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_oth+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>192.918954650496</v>
+        <v>198.382299507535</v>
       </c>
       <c r="D47" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_oth+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_oth+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -51949,7 +52063,7 @@
       </c>
       <c r="C48" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_oth+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_oth+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>192.918954650496</v>
+        <v>198.382299507535</v>
       </c>
       <c r="D48" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_oth+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_oth+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -51978,7 +52092,7 @@
       </c>
       <c r="C49" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_oth+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_oth+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>192.918954650496</v>
+        <v>198.382299507535</v>
       </c>
       <c r="D49" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_oth+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_oth+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_oth)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52007,7 +52121,7 @@
       </c>
       <c r="C50" s="18" t="n">
         <f aca="false">C47/C44-1</f>
-        <v>0.0828589384092797</v>
+        <v>0.0897431067021142</v>
       </c>
       <c r="D50" s="18" t="n">
         <f aca="false">D47/D44-1</f>
@@ -52032,7 +52146,7 @@
       </c>
       <c r="C51" s="18" t="n">
         <f aca="false">C48/C45-1</f>
-        <v>0.0828589384092797</v>
+        <v>0.0897431067021142</v>
       </c>
       <c r="D51" s="18" t="n">
         <f aca="false">D48/D45-1</f>
@@ -52057,7 +52171,7 @@
       </c>
       <c r="C52" s="18" t="n">
         <f aca="false">C49/C46-1</f>
-        <v>0.0828589384092797</v>
+        <v>0.0897431067021142</v>
       </c>
       <c r="D52" s="18" t="n">
         <f aca="false">D49/D46-1</f>
@@ -52113,7 +52227,7 @@
       </c>
       <c r="C57" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="D57" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52142,7 +52256,7 @@
       </c>
       <c r="C58" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="D58" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52171,7 +52285,7 @@
       </c>
       <c r="C59" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="D59" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52200,7 +52314,7 @@
       </c>
       <c r="C60" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>175.355658526185</v>
+        <v>179.243622315359</v>
       </c>
       <c r="D60" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52229,7 +52343,7 @@
       </c>
       <c r="C61" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>175.355658526185</v>
+        <v>179.243622315359</v>
       </c>
       <c r="D61" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52258,7 +52372,7 @@
       </c>
       <c r="C62" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>175.355658526185</v>
+        <v>179.243622315359</v>
       </c>
       <c r="D62" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_lo+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_lo,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52287,7 +52401,7 @@
       </c>
       <c r="C63" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>180.358144318938</v>
+        <v>184.246108108112</v>
       </c>
       <c r="D63" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52316,7 +52430,7 @@
       </c>
       <c r="C64" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>180.358144318938</v>
+        <v>184.246108108112</v>
       </c>
       <c r="D64" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52345,7 +52459,7 @@
       </c>
       <c r="C65" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>180.358144318938</v>
+        <v>184.246108108112</v>
       </c>
       <c r="D65" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_fd_hi+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_fd_hi,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52374,7 +52488,7 @@
       </c>
       <c r="C66" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>174.464275660624</v>
+        <v>178.352239449798</v>
       </c>
       <c r="D66" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52403,7 +52517,7 @@
       </c>
       <c r="C67" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>174.464275660624</v>
+        <v>178.352239449798</v>
       </c>
       <c r="D67" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52432,7 +52546,7 @@
       </c>
       <c r="C68" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>174.464275660624</v>
+        <v>178.352239449798</v>
       </c>
       <c r="D68" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-0)*sh_sk+MAX(Mkt!$C$43-cap_ts_25*(1-0)*sh_sk,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52461,7 +52575,7 @@
       </c>
       <c r="C69" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>176.23609602571</v>
+        <v>180.124059814883</v>
       </c>
       <c r="D69" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52490,7 +52604,7 @@
       </c>
       <c r="C70" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>176.23609602571</v>
+        <v>180.124059814883</v>
       </c>
       <c r="D70" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52519,7 +52633,7 @@
       </c>
       <c r="C71" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>176.23609602571</v>
+        <v>180.124059814883</v>
       </c>
       <c r="D71" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52548,7 +52662,7 @@
       </c>
       <c r="C72" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>175.595777844237</v>
+        <v>179.483741633411</v>
       </c>
       <c r="D72" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52577,7 +52691,7 @@
       </c>
       <c r="C73" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>175.595777844237</v>
+        <v>179.483741633411</v>
       </c>
       <c r="D73" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52606,7 +52720,7 @@
       </c>
       <c r="C74" s="17" t="n">
         <f aca="false">((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^1)+Mkt!D50*(((cap_sk_26*1000/fx*sh_sk+cap_mu_26*sh_mu_26+cap_ss_26*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^1+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^1)+(cap_ts_26*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^1))+Mkt!D116+Mkt!D117</f>
-        <v>175.595777844237</v>
+        <v>179.483741633411</v>
       </c>
       <c r="D74" s="17" t="n">
         <f aca="false">((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^2)+Mkt!E50*(((cap_sk_27*1000/fx*sh_sk+cap_mu_27*sh_mu_27+cap_ss_27*1000/fx*sh_ss)+(((Mkt!$C$57-Mkt!$C$54+ind_cxmt)*sh_oth))*(1+g_oth_dram)^2+((Mkt!$C$61*sh_oth))*(1+g_oth_nand)^2)+(cap_ts_27*(1-pk_ts_hi)*sh_fd+MAX(Mkt!$C$43-cap_ts_25*(1-pk_ts_hi)*sh_fd,0)*(1+g_oth_fd)^2))+Mkt!E116+Mkt!E117</f>
@@ -52635,7 +52749,7 @@
       </c>
       <c r="C75" s="18" t="n">
         <f aca="false">C60/C57-1</f>
-        <v>-0.0157242839111716</v>
+        <v>-0.0153884579250959</v>
       </c>
       <c r="D75" s="18" t="n">
         <f aca="false">D60/D57-1</f>
@@ -52660,7 +52774,7 @@
       </c>
       <c r="C76" s="18" t="n">
         <f aca="false">C61/C58-1</f>
-        <v>-0.0157242839111716</v>
+        <v>-0.0153884579250959</v>
       </c>
       <c r="D76" s="18" t="n">
         <f aca="false">D61/D58-1</f>
@@ -52685,7 +52799,7 @@
       </c>
       <c r="C77" s="18" t="n">
         <f aca="false">C62/C59-1</f>
-        <v>-0.0157242839111716</v>
+        <v>-0.0153884579250959</v>
       </c>
       <c r="D77" s="18" t="n">
         <f aca="false">D62/D59-1</f>
@@ -52710,7 +52824,7 @@
       </c>
       <c r="C78" s="18" t="n">
         <f aca="false">C63/C57-1</f>
-        <v>0.0123547945016347</v>
+        <v>0.0120909312268613</v>
       </c>
       <c r="D78" s="18" t="n">
         <f aca="false">D63/D57-1</f>
@@ -52735,7 +52849,7 @@
       </c>
       <c r="C79" s="18" t="n">
         <f aca="false">C64/C58-1</f>
-        <v>0.0123547945016347</v>
+        <v>0.0120909312268613</v>
       </c>
       <c r="D79" s="18" t="n">
         <f aca="false">D64/D58-1</f>
@@ -52760,7 +52874,7 @@
       </c>
       <c r="C80" s="18" t="n">
         <f aca="false">C65/C59-1</f>
-        <v>0.0123547945016347</v>
+        <v>0.0120909312268613</v>
       </c>
       <c r="D80" s="18" t="n">
         <f aca="false">D65/D59-1</f>
@@ -52785,7 +52899,7 @@
       </c>
       <c r="C81" s="18" t="n">
         <f aca="false">C66/C57-1</f>
-        <v>-0.0207276383263254</v>
+        <v>-0.0202849549189741</v>
       </c>
       <c r="D81" s="18" t="n">
         <f aca="false">D66/D57-1</f>
@@ -52810,7 +52924,7 @@
       </c>
       <c r="C82" s="18" t="n">
         <f aca="false">C67/C58-1</f>
-        <v>-0.0207276383263254</v>
+        <v>-0.0202849549189741</v>
       </c>
       <c r="D82" s="18" t="n">
         <f aca="false">D67/D58-1</f>
@@ -52835,7 +52949,7 @@
       </c>
       <c r="C83" s="18" t="n">
         <f aca="false">C68/C59-1</f>
-        <v>-0.0207276383263254</v>
+        <v>-0.0202849549189741</v>
       </c>
       <c r="D83" s="18" t="n">
         <f aca="false">D68/D59-1</f>
@@ -52860,7 +52974,7 @@
       </c>
       <c r="C84" s="18" t="n">
         <f aca="false">C69/C57-1</f>
-        <v>-0.0107823661105179</v>
+        <v>-0.0105520854343516</v>
       </c>
       <c r="D84" s="18" t="n">
         <f aca="false">D69/D57-1</f>
@@ -52885,7 +52999,7 @@
       </c>
       <c r="C85" s="18" t="n">
         <f aca="false">C70/C58-1</f>
-        <v>-0.0107823661105179</v>
+        <v>-0.0105520854343516</v>
       </c>
       <c r="D85" s="18" t="n">
         <f aca="false">D70/D58-1</f>
@@ -52910,7 +53024,7 @@
       </c>
       <c r="C86" s="18" t="n">
         <f aca="false">C71/C59-1</f>
-        <v>-0.0107823661105179</v>
+        <v>-0.0105520854343516</v>
       </c>
       <c r="D86" s="18" t="n">
         <f aca="false">D71/D59-1</f>
@@ -52935,7 +53049,7 @@
       </c>
       <c r="C87" s="18" t="n">
         <f aca="false">C72/C57-1</f>
-        <v>-0.0143764881473567</v>
+        <v>-0.0140694472458019</v>
       </c>
       <c r="D87" s="18" t="n">
         <f aca="false">D72/D57-1</f>
@@ -52960,7 +53074,7 @@
       </c>
       <c r="C88" s="18" t="n">
         <f aca="false">C73/C58-1</f>
-        <v>-0.0143764881473567</v>
+        <v>-0.0140694472458019</v>
       </c>
       <c r="D88" s="18" t="n">
         <f aca="false">D73/D58-1</f>
@@ -52985,7 +53099,7 @@
       </c>
       <c r="C89" s="18" t="n">
         <f aca="false">C74/C59-1</f>
-        <v>-0.0143764881473567</v>
+        <v>-0.0140694472458019</v>
       </c>
       <c r="D89" s="18" t="n">
         <f aca="false">D74/D59-1</f>
